--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,42 +665,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="17.04296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="17.04296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="8.73046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="12.4765625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.3125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.8984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="20.3359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>記錄受檢勞工於事業單位之受僱日期。</t>
+    <t>【依據：勞工健康保護規則附表】記錄受檢勞工於事業單位之受僱日期。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-employment-date.xlsx
+++ b/StructureDefinition-ext-employment-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
